--- a/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval_by_type.xlsx
@@ -468,22 +468,22 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8571</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="3">
@@ -496,21 +496,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -586,22 +584,22 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="n">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7">
@@ -614,19 +612,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="H7" t="n">
         <v>0.8333</v>
@@ -673,19 +671,19 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -698,22 +696,22 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>0.6667</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
